--- a/data/industry/CFM/Flash Wafer.xlsx
+++ b/data/industry/CFM/Flash Wafer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB144050-A711-47AC-B299-F1DC79561870}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93800A2-990E-4951-AD85-45110ADE6E18}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>Close</t>
+  </si>
+  <si>
+    <t>UTC+8</t>
   </si>
 </sst>
 </file>
@@ -438,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
@@ -3358,7 +3361,7 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E127" s="10">
         <v>19</v>
@@ -3368,6 +3371,351 @@
       </c>
       <c r="G127" s="10">
         <v>19</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B128" s="1">
+        <v>46062</v>
+      </c>
+      <c r="C128" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="10">
+        <v>19</v>
+      </c>
+      <c r="F128" s="10">
+        <v>19</v>
+      </c>
+      <c r="G128" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B129" s="1">
+        <v>46063</v>
+      </c>
+      <c r="C129" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="10">
+        <v>24</v>
+      </c>
+      <c r="F129" s="10">
+        <v>24</v>
+      </c>
+      <c r="G129" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B130" s="1">
+        <v>46064</v>
+      </c>
+      <c r="C130" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="10">
+        <v>24</v>
+      </c>
+      <c r="F130" s="10">
+        <v>24</v>
+      </c>
+      <c r="G130" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B131" s="1">
+        <v>46065</v>
+      </c>
+      <c r="C131" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="10">
+        <v>24</v>
+      </c>
+      <c r="F131" s="10">
+        <v>24</v>
+      </c>
+      <c r="G131" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B132" s="1">
+        <v>46066</v>
+      </c>
+      <c r="C132" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="10">
+        <v>24</v>
+      </c>
+      <c r="F132" s="10">
+        <v>24</v>
+      </c>
+      <c r="G132" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>46067</v>
+      </c>
+      <c r="B133" s="1">
+        <v>46067</v>
+      </c>
+      <c r="C133" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="10">
+        <v>24</v>
+      </c>
+      <c r="F133" s="10">
+        <v>24</v>
+      </c>
+      <c r="G133" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B134" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C134" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="10">
+        <v>24</v>
+      </c>
+      <c r="F134" s="10">
+        <v>24</v>
+      </c>
+      <c r="G134" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B135" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C135" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="10">
+        <v>24</v>
+      </c>
+      <c r="F135" s="10">
+        <v>24</v>
+      </c>
+      <c r="G135" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B136" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C136" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="10">
+        <v>24</v>
+      </c>
+      <c r="F136" s="10">
+        <v>24</v>
+      </c>
+      <c r="G136" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B137" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C137" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="10">
+        <v>24</v>
+      </c>
+      <c r="F137" s="10">
+        <v>24</v>
+      </c>
+      <c r="G137" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B138" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C138" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="10">
+        <v>24</v>
+      </c>
+      <c r="F138" s="10">
+        <v>24</v>
+      </c>
+      <c r="G138" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B139" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C139" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="10">
+        <v>24</v>
+      </c>
+      <c r="F139" s="10">
+        <v>24</v>
+      </c>
+      <c r="G139" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B140" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C140" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="10">
+        <v>24</v>
+      </c>
+      <c r="F140" s="10">
+        <v>24</v>
+      </c>
+      <c r="G140" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B141" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C141" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="10">
+        <v>24</v>
+      </c>
+      <c r="F141" s="10">
+        <v>24</v>
+      </c>
+      <c r="G141" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B142" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C142" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="10">
+        <v>24</v>
+      </c>
+      <c r="F142" s="10">
+        <v>24</v>
+      </c>
+      <c r="G142" s="10">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -3379,7 +3727,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71734CED-25E0-4599-A4D6-BAA4DFE2F205}">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
@@ -6299,7 +6647,7 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E127" s="10">
         <v>20</v>
@@ -6309,6 +6657,351 @@
       </c>
       <c r="G127" s="10">
         <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B128" s="1">
+        <v>46062</v>
+      </c>
+      <c r="C128" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="10">
+        <v>20</v>
+      </c>
+      <c r="F128" s="10">
+        <v>20</v>
+      </c>
+      <c r="G128" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B129" s="1">
+        <v>46063</v>
+      </c>
+      <c r="C129" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="10">
+        <v>25</v>
+      </c>
+      <c r="F129" s="10">
+        <v>25</v>
+      </c>
+      <c r="G129" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B130" s="1">
+        <v>46064</v>
+      </c>
+      <c r="C130" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="10">
+        <v>25</v>
+      </c>
+      <c r="F130" s="10">
+        <v>25</v>
+      </c>
+      <c r="G130" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B131" s="1">
+        <v>46065</v>
+      </c>
+      <c r="C131" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="10">
+        <v>25</v>
+      </c>
+      <c r="F131" s="10">
+        <v>25</v>
+      </c>
+      <c r="G131" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B132" s="1">
+        <v>46066</v>
+      </c>
+      <c r="C132" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="10">
+        <v>25</v>
+      </c>
+      <c r="F132" s="10">
+        <v>25</v>
+      </c>
+      <c r="G132" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>46067</v>
+      </c>
+      <c r="B133" s="1">
+        <v>46067</v>
+      </c>
+      <c r="C133" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="10">
+        <v>25</v>
+      </c>
+      <c r="F133" s="10">
+        <v>25</v>
+      </c>
+      <c r="G133" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B134" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C134" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="10">
+        <v>25</v>
+      </c>
+      <c r="F134" s="10">
+        <v>25</v>
+      </c>
+      <c r="G134" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B135" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C135" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="10">
+        <v>25</v>
+      </c>
+      <c r="F135" s="10">
+        <v>25</v>
+      </c>
+      <c r="G135" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B136" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C136" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="10">
+        <v>25</v>
+      </c>
+      <c r="F136" s="10">
+        <v>25</v>
+      </c>
+      <c r="G136" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B137" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C137" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="10">
+        <v>25</v>
+      </c>
+      <c r="F137" s="10">
+        <v>25</v>
+      </c>
+      <c r="G137" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B138" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C138" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="10">
+        <v>25</v>
+      </c>
+      <c r="F138" s="10">
+        <v>25</v>
+      </c>
+      <c r="G138" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B139" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C139" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="10">
+        <v>25</v>
+      </c>
+      <c r="F139" s="10">
+        <v>25</v>
+      </c>
+      <c r="G139" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B140" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C140" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="10">
+        <v>25</v>
+      </c>
+      <c r="F140" s="10">
+        <v>25</v>
+      </c>
+      <c r="G140" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B141" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C141" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="10">
+        <v>25</v>
+      </c>
+      <c r="F141" s="10">
+        <v>25</v>
+      </c>
+      <c r="G141" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B142" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C142" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="10">
+        <v>25</v>
+      </c>
+      <c r="F142" s="10">
+        <v>25</v>
+      </c>
+      <c r="G142" s="10">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -6319,7 +7012,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DF3FEF-B1BB-46E2-A380-08118BE83F0E}">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
@@ -9239,7 +9932,7 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E127" s="10">
         <v>16</v>
@@ -9249,6 +9942,351 @@
       </c>
       <c r="G127" s="10">
         <v>16</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B128" s="1">
+        <v>46062</v>
+      </c>
+      <c r="C128" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="10">
+        <v>16</v>
+      </c>
+      <c r="F128" s="10">
+        <v>16</v>
+      </c>
+      <c r="G128" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B129" s="1">
+        <v>46063</v>
+      </c>
+      <c r="C129" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="10">
+        <v>20</v>
+      </c>
+      <c r="F129" s="10">
+        <v>20</v>
+      </c>
+      <c r="G129" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B130" s="1">
+        <v>46064</v>
+      </c>
+      <c r="C130" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="10">
+        <v>20</v>
+      </c>
+      <c r="F130" s="10">
+        <v>20</v>
+      </c>
+      <c r="G130" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B131" s="1">
+        <v>46065</v>
+      </c>
+      <c r="C131" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="10">
+        <v>20</v>
+      </c>
+      <c r="F131" s="10">
+        <v>20</v>
+      </c>
+      <c r="G131" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B132" s="1">
+        <v>46066</v>
+      </c>
+      <c r="C132" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="10">
+        <v>20</v>
+      </c>
+      <c r="F132" s="10">
+        <v>20</v>
+      </c>
+      <c r="G132" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>46067</v>
+      </c>
+      <c r="B133" s="1">
+        <v>46067</v>
+      </c>
+      <c r="C133" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="10">
+        <v>20</v>
+      </c>
+      <c r="F133" s="10">
+        <v>20</v>
+      </c>
+      <c r="G133" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B134" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C134" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="10">
+        <v>20</v>
+      </c>
+      <c r="F134" s="10">
+        <v>20</v>
+      </c>
+      <c r="G134" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B135" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C135" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="10">
+        <v>20</v>
+      </c>
+      <c r="F135" s="10">
+        <v>20</v>
+      </c>
+      <c r="G135" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B136" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C136" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="10">
+        <v>20</v>
+      </c>
+      <c r="F136" s="10">
+        <v>20</v>
+      </c>
+      <c r="G136" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B137" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C137" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="10">
+        <v>20</v>
+      </c>
+      <c r="F137" s="10">
+        <v>20</v>
+      </c>
+      <c r="G137" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B138" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C138" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="10">
+        <v>20</v>
+      </c>
+      <c r="F138" s="10">
+        <v>20</v>
+      </c>
+      <c r="G138" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B139" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C139" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="10">
+        <v>20</v>
+      </c>
+      <c r="F139" s="10">
+        <v>20</v>
+      </c>
+      <c r="G139" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B140" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C140" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="10">
+        <v>20</v>
+      </c>
+      <c r="F140" s="10">
+        <v>20</v>
+      </c>
+      <c r="G140" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B141" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C141" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="10">
+        <v>20</v>
+      </c>
+      <c r="F141" s="10">
+        <v>20</v>
+      </c>
+      <c r="G141" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B142" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C142" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="10">
+        <v>20</v>
+      </c>
+      <c r="F142" s="10">
+        <v>20</v>
+      </c>
+      <c r="G142" s="10">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -9259,7 +10297,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9880E409-A6D2-4363-A52D-1827A2E6AA40}">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
@@ -12179,7 +13217,7 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E127" s="10">
         <v>10</v>
@@ -12189,6 +13227,351 @@
       </c>
       <c r="G127" s="10">
         <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B128" s="1">
+        <v>46062</v>
+      </c>
+      <c r="C128" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="10">
+        <v>10</v>
+      </c>
+      <c r="F128" s="10">
+        <v>10</v>
+      </c>
+      <c r="G128" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B129" s="1">
+        <v>46063</v>
+      </c>
+      <c r="C129" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="10">
+        <v>11</v>
+      </c>
+      <c r="F129" s="10">
+        <v>11</v>
+      </c>
+      <c r="G129" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B130" s="1">
+        <v>46064</v>
+      </c>
+      <c r="C130" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="10">
+        <v>11</v>
+      </c>
+      <c r="F130" s="10">
+        <v>11</v>
+      </c>
+      <c r="G130" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B131" s="1">
+        <v>46065</v>
+      </c>
+      <c r="C131" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="10">
+        <v>11</v>
+      </c>
+      <c r="F131" s="10">
+        <v>11</v>
+      </c>
+      <c r="G131" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B132" s="1">
+        <v>46066</v>
+      </c>
+      <c r="C132" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="10">
+        <v>11</v>
+      </c>
+      <c r="F132" s="10">
+        <v>11</v>
+      </c>
+      <c r="G132" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>46067</v>
+      </c>
+      <c r="B133" s="1">
+        <v>46067</v>
+      </c>
+      <c r="C133" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="10">
+        <v>11</v>
+      </c>
+      <c r="F133" s="10">
+        <v>11</v>
+      </c>
+      <c r="G133" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B134" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C134" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="10">
+        <v>11</v>
+      </c>
+      <c r="F134" s="10">
+        <v>11</v>
+      </c>
+      <c r="G134" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B135" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C135" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="10">
+        <v>11</v>
+      </c>
+      <c r="F135" s="10">
+        <v>11</v>
+      </c>
+      <c r="G135" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B136" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C136" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="10">
+        <v>11</v>
+      </c>
+      <c r="F136" s="10">
+        <v>11</v>
+      </c>
+      <c r="G136" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B137" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C137" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="10">
+        <v>11</v>
+      </c>
+      <c r="F137" s="10">
+        <v>11</v>
+      </c>
+      <c r="G137" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B138" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C138" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="10">
+        <v>11</v>
+      </c>
+      <c r="F138" s="10">
+        <v>11</v>
+      </c>
+      <c r="G138" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B139" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C139" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="10">
+        <v>11</v>
+      </c>
+      <c r="F139" s="10">
+        <v>11</v>
+      </c>
+      <c r="G139" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B140" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C140" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="10">
+        <v>11</v>
+      </c>
+      <c r="F140" s="10">
+        <v>11</v>
+      </c>
+      <c r="G140" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B141" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C141" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="10">
+        <v>11</v>
+      </c>
+      <c r="F141" s="10">
+        <v>11</v>
+      </c>
+      <c r="G141" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B142" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C142" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="10">
+        <v>11</v>
+      </c>
+      <c r="F142" s="10">
+        <v>11</v>
+      </c>
+      <c r="G142" s="10">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/CFM/Flash Wafer.xlsx
+++ b/data/industry/CFM/Flash Wafer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93800A2-990E-4951-AD85-45110ADE6E18}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C77821-EA51-43BD-8A53-602CC375ACD2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1TB QLC" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -441,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
@@ -3718,6 +3718,121 @@
         <v>24</v>
       </c>
     </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B143" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C143" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="10">
+        <v>24</v>
+      </c>
+      <c r="F143" s="10">
+        <v>24</v>
+      </c>
+      <c r="G143" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B144" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C144" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="10">
+        <v>28</v>
+      </c>
+      <c r="F144" s="10">
+        <v>28</v>
+      </c>
+      <c r="G144" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B145" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C145" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="10">
+        <v>28</v>
+      </c>
+      <c r="F145" s="10">
+        <v>28</v>
+      </c>
+      <c r="G145" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B146" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C146" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="10">
+        <v>28</v>
+      </c>
+      <c r="F146" s="10">
+        <v>28</v>
+      </c>
+      <c r="G146" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B147" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C147" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="10">
+        <v>28</v>
+      </c>
+      <c r="F147" s="10">
+        <v>28</v>
+      </c>
+      <c r="G147" s="10">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3727,7 +3842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71734CED-25E0-4599-A4D6-BAA4DFE2F205}">
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
@@ -7004,6 +7119,121 @@
         <v>25</v>
       </c>
     </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B143" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C143" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="10">
+        <v>25</v>
+      </c>
+      <c r="F143" s="10">
+        <v>25</v>
+      </c>
+      <c r="G143" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B144" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C144" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="10">
+        <v>29</v>
+      </c>
+      <c r="F144" s="10">
+        <v>29</v>
+      </c>
+      <c r="G144" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B145" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C145" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="10">
+        <v>29</v>
+      </c>
+      <c r="F145" s="10">
+        <v>29</v>
+      </c>
+      <c r="G145" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B146" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C146" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="10">
+        <v>29</v>
+      </c>
+      <c r="F146" s="10">
+        <v>29</v>
+      </c>
+      <c r="G146" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B147" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C147" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="10">
+        <v>29</v>
+      </c>
+      <c r="F147" s="10">
+        <v>29</v>
+      </c>
+      <c r="G147" s="10">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7012,7 +7242,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DF3FEF-B1BB-46E2-A380-08118BE83F0E}">
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
@@ -10289,6 +10519,121 @@
         <v>20</v>
       </c>
     </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B143" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C143" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="10">
+        <v>20</v>
+      </c>
+      <c r="F143" s="10">
+        <v>20</v>
+      </c>
+      <c r="G143" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B144" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C144" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="10">
+        <v>23</v>
+      </c>
+      <c r="F144" s="10">
+        <v>23</v>
+      </c>
+      <c r="G144" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B145" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C145" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="10">
+        <v>23</v>
+      </c>
+      <c r="F145" s="10">
+        <v>23</v>
+      </c>
+      <c r="G145" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B146" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C146" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="10">
+        <v>23</v>
+      </c>
+      <c r="F146" s="10">
+        <v>23</v>
+      </c>
+      <c r="G146" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B147" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C147" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="10">
+        <v>23</v>
+      </c>
+      <c r="F147" s="10">
+        <v>23</v>
+      </c>
+      <c r="G147" s="10">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10297,7 +10642,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9880E409-A6D2-4363-A52D-1827A2E6AA40}">
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
@@ -13574,6 +13919,121 @@
         <v>11</v>
       </c>
     </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B143" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C143" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="10">
+        <v>11</v>
+      </c>
+      <c r="F143" s="10">
+        <v>11</v>
+      </c>
+      <c r="G143" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B144" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C144" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="10">
+        <v>11</v>
+      </c>
+      <c r="F144" s="10">
+        <v>11</v>
+      </c>
+      <c r="G144" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B145" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C145" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="10">
+        <v>11</v>
+      </c>
+      <c r="F145" s="10">
+        <v>11</v>
+      </c>
+      <c r="G145" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B146" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C146" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="10">
+        <v>11</v>
+      </c>
+      <c r="F146" s="10">
+        <v>11</v>
+      </c>
+      <c r="G146" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B147" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C147" s="2">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="10">
+        <v>11</v>
+      </c>
+      <c r="F147" s="10">
+        <v>11</v>
+      </c>
+      <c r="G147" s="10">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/Flash Wafer.xlsx
+++ b/data/industry/CFM/Flash Wafer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470DE96A-BC01-4294-B045-3CF8FE517231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEDD2AA-7C41-467D-9983-4FA0CAFE7661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1TB QLC" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -441,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="1" bestFit="1" customWidth="1"/>
@@ -4109,6 +4109,75 @@
         <v>27</v>
       </c>
     </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B160" s="1">
+        <v>46136</v>
+      </c>
+      <c r="C160" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E160" s="10">
+        <v>27</v>
+      </c>
+      <c r="F160" s="10">
+        <v>27</v>
+      </c>
+      <c r="G160" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B161" s="1">
+        <v>46140</v>
+      </c>
+      <c r="C161" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E161" s="10">
+        <v>27</v>
+      </c>
+      <c r="F161" s="10">
+        <v>27</v>
+      </c>
+      <c r="G161" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B162" s="1">
+        <v>46142</v>
+      </c>
+      <c r="C162" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E162" s="10">
+        <v>27</v>
+      </c>
+      <c r="F162" s="10">
+        <v>27</v>
+      </c>
+      <c r="G162" s="10">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4118,7 +4187,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71734CED-25E0-4599-A4D6-BAA4DFE2F205}">
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="1" bestFit="1" customWidth="1"/>
@@ -7786,6 +7855,75 @@
         <v>29</v>
       </c>
     </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B160" s="1">
+        <v>46136</v>
+      </c>
+      <c r="C160" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E160" s="10">
+        <v>29</v>
+      </c>
+      <c r="F160" s="10">
+        <v>29</v>
+      </c>
+      <c r="G160" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B161" s="1">
+        <v>46140</v>
+      </c>
+      <c r="C161" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E161" s="10">
+        <v>29</v>
+      </c>
+      <c r="F161" s="10">
+        <v>29</v>
+      </c>
+      <c r="G161" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B162" s="1">
+        <v>46142</v>
+      </c>
+      <c r="C162" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E162" s="10">
+        <v>29</v>
+      </c>
+      <c r="F162" s="10">
+        <v>29</v>
+      </c>
+      <c r="G162" s="10">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7794,7 +7932,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DF3FEF-B1BB-46E2-A380-08118BE83F0E}">
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="1" bestFit="1" customWidth="1"/>
@@ -11462,6 +11600,75 @@
         <v>23</v>
       </c>
     </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B160" s="1">
+        <v>46136</v>
+      </c>
+      <c r="C160" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E160" s="10">
+        <v>23</v>
+      </c>
+      <c r="F160" s="10">
+        <v>23</v>
+      </c>
+      <c r="G160" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B161" s="1">
+        <v>46140</v>
+      </c>
+      <c r="C161" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E161" s="10">
+        <v>23</v>
+      </c>
+      <c r="F161" s="10">
+        <v>23</v>
+      </c>
+      <c r="G161" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B162" s="1">
+        <v>46142</v>
+      </c>
+      <c r="C162" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E162" s="10">
+        <v>23</v>
+      </c>
+      <c r="F162" s="10">
+        <v>23</v>
+      </c>
+      <c r="G162" s="10">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11470,7 +11677,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9880E409-A6D2-4363-A52D-1827A2E6AA40}">
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="1" bestFit="1" customWidth="1"/>
@@ -15138,6 +15345,75 @@
         <v>11</v>
       </c>
     </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B160" s="1">
+        <v>46136</v>
+      </c>
+      <c r="C160" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E160" s="10">
+        <v>11</v>
+      </c>
+      <c r="F160" s="10">
+        <v>11</v>
+      </c>
+      <c r="G160" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B161" s="1">
+        <v>46140</v>
+      </c>
+      <c r="C161" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E161" s="10">
+        <v>11</v>
+      </c>
+      <c r="F161" s="10">
+        <v>11</v>
+      </c>
+      <c r="G161" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B162" s="1">
+        <v>46142</v>
+      </c>
+      <c r="C162" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E162" s="10">
+        <v>11</v>
+      </c>
+      <c r="F162" s="10">
+        <v>11</v>
+      </c>
+      <c r="G162" s="10">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
